--- a/project/res/result/tabela_resultados.xlsx
+++ b/project/res/result/tabela_resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +842,170 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vídeo 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00_00_00_100</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5, 6, 12</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3.669236421585083</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>294.0</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vídeo 2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00_00_00_00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5, 6, 12</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1.555630922317505</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7377.5</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vídeo 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00_00_00_100</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5, 6, 12</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3.068687438964844</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>294.0</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vídeo 2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GORDURA SATURADA</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00_00_00_00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5, 6, 12</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1.446971416473389</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7377.5</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
